--- a/research/traditional_assets/database/data/pakistan/pakistan_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/pakistan/pakistan_banks_regional.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.102</v>
+        <v>0.0992</v>
       </c>
       <c r="E2">
-        <v>-0.14</v>
+        <v>-0.0684</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,10 +606,10 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>6.04</v>
+        <v>4.89</v>
       </c>
       <c r="L2">
-        <v>0.06156982670744139</v>
+        <v>0.05941676792223572</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -633,55 +633,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>147</v>
+        <v>139.8</v>
       </c>
       <c r="V2">
-        <v>4.140845070422535</v>
+        <v>5.197026022304834</v>
       </c>
       <c r="W2">
-        <v>0.04603658536585366</v>
+        <v>0.03500357909806729</v>
       </c>
       <c r="X2">
-        <v>0.6976417885948051</v>
+        <v>0.6246004595394734</v>
       </c>
       <c r="Y2">
-        <v>-0.6516052032289514</v>
+        <v>-0.5895968804414061</v>
       </c>
       <c r="Z2">
-        <v>0.4678780941479468</v>
+        <v>0.1939116912492342</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1037539502396767</v>
+        <v>0.1437186588453233</v>
       </c>
       <c r="AC2">
-        <v>-0.1037539502396767</v>
+        <v>-0.1437186588453233</v>
       </c>
       <c r="AD2">
-        <v>440.3</v>
+        <v>287.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>440.3</v>
+        <v>287.5</v>
       </c>
       <c r="AG2">
-        <v>293.3</v>
+        <v>147.7</v>
       </c>
       <c r="AH2">
-        <v>0.9253888188314418</v>
+        <v>0.914440203562341</v>
       </c>
       <c r="AI2">
-        <v>0.7571797076526225</v>
+        <v>0.7336055116101047</v>
       </c>
       <c r="AJ2">
-        <v>0.8920316301703163</v>
+        <v>0.8459335624284078</v>
       </c>
       <c r="AK2">
-        <v>0.6750287686996548</v>
+        <v>0.5858786195953987</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.102</v>
+        <v>0.0992</v>
       </c>
       <c r="E3">
-        <v>-0.14</v>
+        <v>-0.0684</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -725,10 +725,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>6.04</v>
+        <v>4.89</v>
       </c>
       <c r="L3">
-        <v>0.06156982670744139</v>
+        <v>0.05941676792223572</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,55 +752,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>147</v>
+        <v>139.8</v>
       </c>
       <c r="V3">
-        <v>4.140845070422535</v>
+        <v>5.197026022304834</v>
       </c>
       <c r="W3">
-        <v>0.04603658536585366</v>
+        <v>0.03500357909806729</v>
       </c>
       <c r="X3">
-        <v>0.6976417885948051</v>
+        <v>0.6246004595394734</v>
       </c>
       <c r="Y3">
-        <v>-0.6516052032289514</v>
+        <v>-0.5895968804414061</v>
       </c>
       <c r="Z3">
-        <v>0.4678780941479468</v>
+        <v>0.1939116912492342</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.1037539502396767</v>
+        <v>0.1437186588453233</v>
       </c>
       <c r="AC3">
-        <v>-0.1037539502396767</v>
+        <v>-0.1437186588453233</v>
       </c>
       <c r="AD3">
-        <v>440.3</v>
+        <v>287.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>440.3</v>
+        <v>287.5</v>
       </c>
       <c r="AG3">
-        <v>293.3</v>
+        <v>147.7</v>
       </c>
       <c r="AH3">
-        <v>0.9253888188314418</v>
+        <v>0.914440203562341</v>
       </c>
       <c r="AI3">
-        <v>0.7571797076526225</v>
+        <v>0.7336055116101047</v>
       </c>
       <c r="AJ3">
-        <v>0.8920316301703163</v>
+        <v>0.8459335624284078</v>
       </c>
       <c r="AK3">
-        <v>0.6750287686996548</v>
+        <v>0.5858786195953987</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/pakistan/pakistan_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/pakistan/pakistan_banks_regional.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0992</v>
+        <v>0.208</v>
       </c>
       <c r="E2">
-        <v>-0.0684</v>
+        <v>0.389</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,10 +606,10 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>4.89</v>
+        <v>23.9</v>
       </c>
       <c r="L2">
-        <v>0.05941676792223572</v>
+        <v>0.2056798623063683</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -633,55 +633,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>139.8</v>
+        <v>259.6</v>
       </c>
       <c r="V2">
-        <v>5.197026022304834</v>
+        <v>3.756874095513749</v>
       </c>
       <c r="W2">
-        <v>0.03500357909806729</v>
+        <v>0.2324902723735408</v>
       </c>
       <c r="X2">
-        <v>0.6246004595394734</v>
+        <v>0.327009983792249</v>
       </c>
       <c r="Y2">
-        <v>-0.5895968804414061</v>
+        <v>-0.09451971141870816</v>
       </c>
       <c r="Z2">
-        <v>0.1939116912492342</v>
+        <v>0.476053914539719</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1437186588453233</v>
+        <v>0.1413339678837493</v>
       </c>
       <c r="AC2">
-        <v>-0.1437186588453233</v>
+        <v>-0.1413339678837493</v>
       </c>
       <c r="AD2">
-        <v>287.5</v>
+        <v>401.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>287.5</v>
+        <v>401.1</v>
       </c>
       <c r="AG2">
-        <v>147.7</v>
+        <v>141.5</v>
       </c>
       <c r="AH2">
-        <v>0.914440203562341</v>
+        <v>0.8530412590387069</v>
       </c>
       <c r="AI2">
-        <v>0.7336055116101047</v>
+        <v>0.6869326939544442</v>
       </c>
       <c r="AJ2">
-        <v>0.8459335624284078</v>
+        <v>0.6718898385565052</v>
       </c>
       <c r="AK2">
-        <v>0.5858786195953987</v>
+        <v>0.4363243909959914</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0992</v>
+        <v>0.208</v>
       </c>
       <c r="E3">
-        <v>-0.0684</v>
+        <v>0.389</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -725,10 +725,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>4.89</v>
+        <v>23.9</v>
       </c>
       <c r="L3">
-        <v>0.05941676792223572</v>
+        <v>0.2056798623063683</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,55 +752,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>139.8</v>
+        <v>259.6</v>
       </c>
       <c r="V3">
-        <v>5.197026022304834</v>
+        <v>3.756874095513749</v>
       </c>
       <c r="W3">
-        <v>0.03500357909806729</v>
+        <v>0.2324902723735408</v>
       </c>
       <c r="X3">
-        <v>0.6246004595394734</v>
+        <v>0.327009983792249</v>
       </c>
       <c r="Y3">
-        <v>-0.5895968804414061</v>
+        <v>-0.09451971141870816</v>
       </c>
       <c r="Z3">
-        <v>0.1939116912492342</v>
+        <v>0.476053914539719</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.1437186588453233</v>
+        <v>0.1413339678837493</v>
       </c>
       <c r="AC3">
-        <v>-0.1437186588453233</v>
+        <v>-0.1413339678837493</v>
       </c>
       <c r="AD3">
-        <v>287.5</v>
+        <v>401.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>287.5</v>
+        <v>401.1</v>
       </c>
       <c r="AG3">
-        <v>147.7</v>
+        <v>141.5</v>
       </c>
       <c r="AH3">
-        <v>0.914440203562341</v>
+        <v>0.8530412590387069</v>
       </c>
       <c r="AI3">
-        <v>0.7336055116101047</v>
+        <v>0.6869326939544442</v>
       </c>
       <c r="AJ3">
-        <v>0.8459335624284078</v>
+        <v>0.6718898385565052</v>
       </c>
       <c r="AK3">
-        <v>0.5858786195953987</v>
+        <v>0.4363243909959914</v>
       </c>
       <c r="AL3">
         <v>0</v>
